--- a/(붙임2) AI활용대체시장정보_신청양식_부서명.xlsx
+++ b/(붙임2) AI활용대체시장정보_신청양식_부서명.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ki/Documents/KOTRA_Report_Auto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0D4E00-9AC8-9042-89AE-5F55C404514A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9355ADF5-65AC-9147-9164-7E012BB752EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{B46CDF17-D3C1-4690-97F2-2CDBAC0D0B10}"/>
   </bookViews>
@@ -642,10 +642,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이스라엘</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>부서/무역관명</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -682,6 +678,10 @@
   </si>
   <si>
     <t>초보기업 ($1~$99,999)</t>
+  </si>
+  <si>
+    <t>이스라엘, 일본</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1169,7 +1169,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
@@ -1178,10 +1178,10 @@
         <v>1</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>2</v>
@@ -1193,10 +1193,10 @@
         <v>3</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -1226,10 +1226,10 @@
         <v>6</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1245,7 +1245,7 @@
         <v>9</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>6</v>
@@ -1254,7 +1254,7 @@
         <v>17</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1268,7 +1268,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K4" s="1"/>
     </row>
